--- a/output/pdf_financials_xlsx/GAR.H.xlsx
+++ b/output/pdf_financials_xlsx/GAR.H.xlsx
@@ -1376,10 +1376,10 @@
         <v>0.220436</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.636432</v>
+        <v>-0.636432</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.283926</v>
+        <v>-0.283926</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.18807</v>
@@ -1388,19 +1388,19 @@
         <v>-0.118004</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.14484</v>
+        <v>-0.14484</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.07656399999999999</v>
+        <v>-0.07656399999999999</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.110087</v>
+        <v>-0.110087</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.077532</v>
+        <v>-0.077532</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.065056</v>
+        <v>-0.065056</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-0.102592</v>
@@ -1435,7 +1435,7 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.09615</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0.856868</v>
@@ -1694,16 +1694,16 @@
         <v>-0.037408</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.048075</v>
+        <v>-0.048075</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.636432</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.636432</v>
+        <v>-0.636432</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.283926</v>
+        <v>-0.283926</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.18807</v>
@@ -1712,19 +1712,19 @@
         <v>-0.118004</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.14484</v>
+        <v>-0.14484</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.07656399999999999</v>
+        <v>-0.07656399999999999</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.110087</v>
+        <v>-0.110087</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.077532</v>
+        <v>-0.077532</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.065056</v>
+        <v>-0.065056</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>-0.102592</v>
@@ -1889,16 +1889,16 @@
         <v>-0.037408</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.048075</v>
+        <v>-0.048075</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.636432</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.636432</v>
+        <v>-0.636432</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.283926</v>
+        <v>-0.283926</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.18807</v>
@@ -1907,19 +1907,19 @@
         <v>-0.118004</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.14484</v>
+        <v>-0.14484</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.07656399999999999</v>
+        <v>-0.07656399999999999</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.110087</v>
+        <v>-0.110087</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.077532</v>
+        <v>-0.077532</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.065056</v>
+        <v>-0.065056</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>-0.102592</v>
@@ -2112,10 +2112,10 @@
         <v>-38.339277</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2.6518</v>
+        <v>-2.6518</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>3.549075</v>
+        <v>-3.549075</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
         <v>0.220436</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.636432</v>
+        <v>-0.636432</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.283926</v>
+        <v>-0.283926</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.18807</v>
@@ -2209,19 +2209,19 @@
         <v>-0.118004</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.14484</v>
+        <v>-0.14484</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.07656399999999999</v>
+        <v>-0.07656399999999999</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.110087</v>
+        <v>-0.110087</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.077532</v>
+        <v>-0.077532</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.065056</v>
+        <v>-0.065056</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.102592</v>
@@ -2327,10 +2327,10 @@
         <v>0.220436</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.636432</v>
+        <v>-0.636432</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.283926</v>
+        <v>-0.283926</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.18807</v>
@@ -2339,19 +2339,19 @@
         <v>-0.118004</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.14484</v>
+        <v>-0.14484</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.07656399999999999</v>
+        <v>-0.07656399999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.110087</v>
+        <v>-0.110087</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.077532</v>
+        <v>-0.077532</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.065056</v>
+        <v>-0.065056</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.102592</v>
@@ -2483,16 +2483,16 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>388.7150919087626</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -2501,19 +2501,19 @@
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -6611,22 +6611,22 @@
         <v>0.06215</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.073559</v>
+        <v>0.036119</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.039619</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.0183</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.0173</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.0173</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.015687</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -7286,13 +7286,13 @@
         <v>0</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.093431</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.051643</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         <v>0.002141</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.000959</v>
+        <v>-0.092472</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.142235</v>
+        <v>0.193878</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.092364</v>
+        <v>0.145364</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>0.184051</v>
@@ -12360,7 +12360,11 @@
           <t>Warrant reserves (note 6)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -13410,7 +13414,11 @@
           <t>Warrant reserve (note 8(c )</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -14470,7 +14478,11 @@
           <t>Warrant reserve (note 7(c))</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -15002,7 +15014,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -15754,7 +15770,11 @@
           <t>Warrant Reserve (note 9(d))</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -16398,7 +16418,11 @@
           <t>Prepaids and deposits 53,000</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -17250,7 +17274,11 @@
           <t>Warrant Reserve (note 9 (d)) 39,619</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -17996,7 +18024,11 @@
           <t>Prepaids and deposits 104,643</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -18864,7 +18896,11 @@
           <t>Reserve for Warrants (note 9(e)) 36,119</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -28214,7 +28250,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -30044,7 +30084,11 @@
           <t>Prepaids and deposits 51,643</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -38920,13 +38964,13 @@
         </is>
       </c>
       <c r="Q277" s="5" t="n">
-        <v>0.077532</v>
+        <v>-0.077532</v>
       </c>
       <c r="R277" s="5" t="n">
-        <v>0.065056</v>
+        <v>-0.065056</v>
       </c>
       <c r="S277" s="5" t="n">
-        <v>0.102592</v>
+        <v>-0.102592</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -39540,13 +39584,13 @@
         </is>
       </c>
       <c r="O283" s="5" t="n">
-        <v>0.07656399999999999</v>
+        <v>-0.07656399999999999</v>
       </c>
       <c r="P283" s="5" t="n">
-        <v>0.110087</v>
+        <v>-0.110087</v>
       </c>
       <c r="Q283" s="5" t="n">
-        <v>0.077532</v>
+        <v>-0.077532</v>
       </c>
       <c r="R283" t="inlineStr">
         <is>
@@ -41859,10 +41903,10 @@
         </is>
       </c>
       <c r="N305" s="5" t="n">
-        <v>0.14484</v>
+        <v>-0.14484</v>
       </c>
       <c r="O305" s="5" t="n">
-        <v>0.07656399999999999</v>
+        <v>-0.07656399999999999</v>
       </c>
       <c r="P305" t="inlineStr">
         <is>
@@ -46805,10 +46849,10 @@
         </is>
       </c>
       <c r="J352" s="5" t="n">
-        <v>0.636432</v>
+        <v>-0.636432</v>
       </c>
       <c r="K352" s="5" t="n">
-        <v>0.283926</v>
+        <v>-0.283926</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -54473,10 +54517,10 @@
         </is>
       </c>
       <c r="H424" s="5" t="n">
-        <v>0.048075</v>
+        <v>-0.048075</v>
       </c>
       <c r="I424" s="5" t="n">
-        <v>0.220436</v>
+        <v>-0.220436</v>
       </c>
       <c r="J424" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GAR.H.xlsx
+++ b/output/pdf_financials_xlsx/GAR.H.xlsx
@@ -1019,7 +1019,7 @@
         <v>0.101961</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.069393</v>
+        <v>0.078393</v>
       </c>
       <c r="S10" s="1" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>-0.101961</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.069393</v>
+        <v>-0.078393</v>
       </c>
       <c r="S11" s="1" t="inlineStr">
         <is>
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>7.1e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000453</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000801</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000679</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2185,16 +2185,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.020674</v>
+        <v>-0.020745</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.037408</v>
+        <v>-0.037861</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.048075</v>
+        <v>0.047274</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.220436</v>
+        <v>0.221115</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.636432</v>
@@ -2315,16 +2315,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.020674</v>
+        <v>-0.020745</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.037408</v>
+        <v>-0.037861</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.048075</v>
+        <v>0.047274</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.220436</v>
+        <v>0.221115</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.636432</v>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.122383</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.744101</v>
@@ -2658,40 +2658,40 @@
         <v>0.773153</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.013193</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.070377</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.5e-05</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.00254</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.002436</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.001541</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.001516</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.00146</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.003278</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.000146</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000304</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.000225</v>
       </c>
       <c r="S34" s="1" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.122383</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.744101</v>
@@ -2788,40 +2788,40 @@
         <v>0.773153</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.013193</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.070377</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.5e-05</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.00254</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.002436</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.001541</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.001516</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.00146</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.003278</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.000146</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000304</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.000225</v>
       </c>
       <c r="S36" s="1" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.212065</v>
+        <v>0.089682</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.010717</v>
@@ -3568,37 +3568,37 @@
         <v>0.093431</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.066193</v>
+        <v>0.053</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.070377</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.5e-05</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.10254</v>
+        <v>0.1</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.102481</v>
+        <v>0.100045</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.002288</v>
+        <v>0.0007470000000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.002329</v>
+        <v>0.000813</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.002524</v>
+        <v>0.001064</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.005193</v>
+        <v>0.001915</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.003314</v>
+        <v>0.003168</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.000304</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -16204,7 +16204,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -36086,7 +36086,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -49162,7 +49162,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -54282,7 +54282,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -55680,7 +55680,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">

--- a/output/pdf_financials_xlsx/GAR.H.xlsx
+++ b/output/pdf_financials_xlsx/GAR.H.xlsx
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.000483</v>
+        <v>0.001042</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.00032</v>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.002863</v>
+        <v>0.003422</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.00032</v>
@@ -1376,10 +1376,10 @@
         <v>0.220436</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.636432</v>
+        <v>0.006163</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-0.283926</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.18807</v>
@@ -1438,13 +1438,13 @@
         <v>-0.09615</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.856868</v>
+        <v>-0.220436</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.642595</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.283926</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -2197,10 +2197,10 @@
         <v>0.221115</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.636432</v>
+        <v>0.006163</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.283926</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.18807</v>
@@ -2327,10 +2327,10 @@
         <v>0.221115</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.636432</v>
+        <v>0.006163</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.283926</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.18807</v>
@@ -2486,13 +2486,15 @@
         <v>200</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>388.7150919087626</v>
+        <v>100</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>10426.65909459679</v>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -4702,22 +4704,22 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.669206</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.647434</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.7124470000000001</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.809872</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.881493</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.964601</v>
       </c>
       <c r="S64" s="1" t="inlineStr">
         <is>
@@ -4885,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -4894,25 +4896,25 @@
         <v>0</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.009712</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="S67" s="1" t="inlineStr">
         <is>
@@ -7174,7 +7176,7 @@
         <v>0.00127</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000702</v>
       </c>
       <c r="M101" s="3" t="n">
         <v>0</v>
@@ -7189,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>0.002865</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000794</v>
       </c>
       <c r="S101" s="1" t="inlineStr">
         <is>
@@ -7514,10 +7516,10 @@
         <v>0.100713</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.071621</v>
+        <v>0.074486</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0.079108</v>
+        <v>0.07831399999999999</v>
       </c>
       <c r="S106" s="1" t="inlineStr">
         <is>
@@ -21780,7 +21782,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -23450,7 +23456,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -24928,7 +24938,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -27926,7 +27940,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -29760,7 +29778,11 @@
           <t>Deferred income tax recovery (6,163)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -46608,7 +46630,11 @@
           <t>Loss Before Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -46712,7 +46738,11 @@
           <t>Deferred Income Tax Recovery (notes 8 and 10(e))</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -49486,7 +49516,11 @@
           <t>Loss Before Deferred Income Tax Recovery 642,595</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -52144,7 +52178,11 @@
           <t>Loss Before Deferred Income Tax Recovery 227,401</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -55464,7 +55502,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
